--- a/artfynd/A 18156-2019 artfynd.xlsx
+++ b/artfynd/A 18156-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18156-2019 artfynd.xlsx
+++ b/artfynd/A 18156-2019 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118704257</v>
+        <v>118704259</v>
       </c>
       <c r="B3" t="n">
-        <v>91232</v>
+        <v>90749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118704259</v>
+        <v>118704257</v>
       </c>
       <c r="B4" t="n">
-        <v>90749</v>
+        <v>91232</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 18156-2019 artfynd.xlsx
+++ b/artfynd/A 18156-2019 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118704259</v>
+        <v>118704257</v>
       </c>
       <c r="B3" t="n">
-        <v>90749</v>
+        <v>91239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>1105</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118704257</v>
+        <v>118704259</v>
       </c>
       <c r="B4" t="n">
-        <v>91232</v>
+        <v>90756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,21 +921,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
